--- a/medical_application_forms/034_medicare_wellness_checkup_form--medical_application_forms.xlsx
+++ b/medical_application_forms/034_medicare_wellness_checkup_form--medical_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -965,12 +965,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>medical_conditions_list</t>
+          <t>medical_conditions_list_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Medical Conditions List</t>
+          <t>Medical Conditions List 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>City</t>
+          <t>Patient City</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Patient State</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Zip</t>
+          <t>Patient Zip</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1109,9 +1109,9 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'abc_medical_group'}</t>
+          <t>abc_medical_group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'ABC Medical Group'}</t>
+          <t>ABC Medical Group</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'def_medical_group'}</t>
+          <t>def_medical_group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'DEF Medical Group'}</t>
+          <t>DEF Medical Group</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'a',_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'A', 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'b',_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'B', 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'a',_'label':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'A', 'label': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'b',_'label':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'B', 'label': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'text':_'c',_'label':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'text': 'C', 'label': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'provider_1',_'label':_'provider_1'}</t>
+          <t>provider_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Provider 1', 'label': 'Provider 1'}</t>
+          <t>Provider 1</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'provider_2',_'label':_'provider_2'}</t>
+          <t>provider_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Provider 2', 'label': 'Provider 2'}</t>
+          <t>Provider 2</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'text':_'condition_1',_'label':_'condition_1'}</t>
+          <t>condition_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'text': 'Condition 1', 'label': 'Condition 1'}</t>
+          <t>Condition 1</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'text':_'condition_2',_'label':_'condition_2'}</t>
+          <t>condition_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'text': 'Condition 2', 'label': 'Condition 2'}</t>
+          <t>Condition 2</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>medical_conditions_list_choices</t>
+          <t>medical_conditions_list_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>medical_conditions_list_choices</t>
+          <t>medical_conditions_list_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
